--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,12 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568844.7637214399</v>
+        <v>568845</v>
       </c>
       <c r="R3" t="n">
-        <v>6293484.712840022</v>
+        <v>6293485</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -871,19 +866,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105725</v>
+        <v>105734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105734</v>
+        <v>105739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105739</v>
+        <v>105767</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105767</v>
+        <v>105773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105773</v>
+        <v>105780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105780</v>
+        <v>105784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105784</v>
+        <v>105791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105794</v>
+        <v>105799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105799</v>
+        <v>105807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14343-2021 artfynd.xlsx
+++ b/artfynd/A 14343-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>74430121</v>
       </c>
       <c r="B3" t="n">
-        <v>105807</v>
+        <v>105817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
